--- a/AAII_Financials/Quarterly/AMGN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMGN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>AMGN</t>
   </si>
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10054000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8618000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9866000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9557000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9179000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8149000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9086000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8503000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8388000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7447000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8196000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6903000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6986000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6105000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6839000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6652000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6594000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6238000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6846000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6706000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6526000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5901000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6634000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6423000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6206000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6161000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6197000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5737000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5871000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5557000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6230000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5904000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6059000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5554000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5802000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5773000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5810000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5464000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5965000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5811000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2751000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2497000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2676000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2744000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2672000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2605000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2712000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2649000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2576000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2507000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2456000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1806000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1813000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1720000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1747000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1588000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1510000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1561000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1718000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1609000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1637000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1490000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1597000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1561000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1488000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1513000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1253000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1036000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1012000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1055000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1096000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1037000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1024000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>944000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1059000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>990000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1024000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>996000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1067000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1027000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7303000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6121000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7190000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6813000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6507000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5544000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6374000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>5854000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>5812000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4940000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5740000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5097000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5173000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4385000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5092000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5064000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5084000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4677000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5128000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5097000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4889000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4411000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5037000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4862000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4718000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4648000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>4944000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4701000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4859000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4502000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5134000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4867000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5035000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4610000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4743000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>4783000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4786000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4468000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>4898000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>4784000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1211,130 +1223,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1868000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1719000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2142000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1744000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1486000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1724000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1450000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1447000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1343000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1534000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1079000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1113000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1324000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1112000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1039000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>959000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1348000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1422000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1082000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>967000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1229000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1062000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>964000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>952000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1312000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1001000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>924000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>879000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1182000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>926000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>869000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>760000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1043000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>877000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>873000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>769000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1078000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>990000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1455,8 +1471,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1464,52 +1483,52 @@
         <v>287000</v>
       </c>
       <c r="E14" s="3">
+        <v>287000</v>
+      </c>
+      <c r="F14" s="3">
         <v>995000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1200000</v>
       </c>
-      <c r="G14" s="3">
-        <v>801000</v>
-      </c>
       <c r="H14" s="3">
+        <v>792000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-648000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1135000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1058000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1058000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1199000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1597000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-330000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-728000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1705000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-73000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>560000</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
@@ -1523,8 +1542,8 @@
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1535,8 +1554,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
@@ -1547,8 +1566,8 @@
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1557,10 +1576,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-80000</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>10</v>
@@ -1571,59 +1590,62 @@
       <c r="AN14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1116000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1008000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1307000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1341000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1387000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1286000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1396000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1400000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1399000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1241000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>895000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>896000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>900000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1699,8 +1721,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,252 +1765,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6480000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5705000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6852000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6293000</v>
       </c>
-      <c r="G17" s="3">
-        <v>6175000</v>
-      </c>
       <c r="H17" s="3">
+        <v>6184000</v>
+      </c>
+      <c r="I17" s="3">
         <v>5808000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6486000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5795000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5681000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5695000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4999000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5029000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4325000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4036000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4609000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3914000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4418000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3738000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4542000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4328000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5698000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3772000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4626000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3970000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3883000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3806000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4149000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3261000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3193000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3085000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3848000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3581000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3227000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2748000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3557000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3334000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3112000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2873000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3480000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3284000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3574000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2913000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3014000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3264000</v>
       </c>
-      <c r="G18" s="3">
-        <v>3004000</v>
-      </c>
       <c r="H18" s="3">
+        <v>2995000</v>
+      </c>
+      <c r="I18" s="3">
         <v>2341000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2600000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2708000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2707000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1752000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3197000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1874000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2661000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2069000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2230000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2738000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2176000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2500000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2304000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2378000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>828000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2129000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2008000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2453000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2323000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2355000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2048000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2476000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2678000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2472000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2382000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2323000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2832000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2806000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2245000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2439000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2698000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2591000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2485000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2527000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2028,618 +2060,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-115000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-148000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-142000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-59000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>293000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-64000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-111000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>47000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-203000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-73000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-502000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1023000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-211000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-67000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>22000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-317000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-530000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>162000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>73000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>13000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>187000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>55000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>11000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>236000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>114000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>218000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>185000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>155000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>126000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>162000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>151000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>301000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>267000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>165000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>195000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>126000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>216000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4840000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4144000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4170000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4713000</v>
       </c>
-      <c r="G21" s="3">
-        <v>4404000</v>
-      </c>
       <c r="H21" s="3">
+        <v>4395000</v>
+      </c>
+      <c r="I21" s="3">
         <v>3435000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3950000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4215000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4060000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3354000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4511000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3271000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2534000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3180000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3074000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3597000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2687000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2811000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3318000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3301000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1694000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2983000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3068000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3409000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3256000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3263000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2986000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3098000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3397000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3152000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3027000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2950000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3478000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3428000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2995000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3170000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3381000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3310000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3170000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3246000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>673000</v>
+      </c>
+      <c r="E22" s="3">
         <v>657000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1061000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>685000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>694000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>723000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1257000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>776000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>808000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>824000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2021000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>759000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>752000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>543000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>415000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>368000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>328000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>295000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>335000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>296000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>281000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>285000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>318000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>302000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>296000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>346000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>301000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>313000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>332000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>343000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>352000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>355000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>347000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>338000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>332000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>325000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>321000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>326000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>328000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>325000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2768000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2084000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1514000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3921000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1568000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1973000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>782000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3101000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>794000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-68000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>852000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1947000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1614000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3442000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1748000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2392000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1531000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1675000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2131000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2155000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>558000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1857000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1877000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2206000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2030000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2020000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1983000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2277000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2564000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2314000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2185000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2094000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2647000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2619000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2214000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2381000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2542000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2460000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2283000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2418000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E24" s="3">
         <v>265000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>181000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>705000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>136000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>243000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>155000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>271000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>48000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>85000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>217000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>235000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>601000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>132000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>249000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>214000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>199000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>232000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>271000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>94000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>211000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>262000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>185000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>227000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>195000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>280000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>309000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>385000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>322000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>257000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>235000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>351000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>308000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>378000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>360000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>391000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>389000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>348000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2760,252 +2808,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1819000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1333000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3216000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1432000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1730000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>627000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2830000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>746000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-113000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>767000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1730000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1379000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2841000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1616000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2143000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1317000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1476000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1899000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1884000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>464000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1646000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2021000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1803000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1703000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1968000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2179000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1992000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1928000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1859000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2311000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1836000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2021000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2151000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1935000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2017000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1819000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1333000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3216000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1432000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1730000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>627000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2830000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>746000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-113000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>767000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1730000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1379000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2841000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1616000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2143000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1317000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1476000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1899000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1884000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>464000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1646000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2021000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1803000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1703000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1968000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2179000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1992000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1928000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1859000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2311000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1836000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2021000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2151000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1935000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>2017000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3126,8 +3183,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3212,8 +3272,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -3230,11 +3290,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-6100000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3248,8 +3308,11 @@
       <c r="AP29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3492,252 +3558,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E32" s="3">
         <v>115000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>148000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>142000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>59000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-293000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>64000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>111000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-47000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>203000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>73000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>502000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1023000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>211000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>67000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-22000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>317000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>530000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-162000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-73000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-187000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-236000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-114000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-185000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-151000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-301000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-267000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-165000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-195000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-216000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1819000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1333000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3216000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1432000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1730000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>627000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2830000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>746000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-113000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>767000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1730000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1379000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2841000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1616000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2143000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1317000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1476000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1899000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1884000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>464000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1646000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2021000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1803000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1703000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1968000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2179000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1992000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1928000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1859000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2311000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-4264000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2021000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2151000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1935000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>2017000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3858,257 +3933,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1819000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1333000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3216000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1432000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1730000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>627000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2830000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>746000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-113000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>767000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1730000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1379000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2841000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1616000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2143000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1317000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1476000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1899000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1884000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>464000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1646000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2021000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1803000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1703000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1968000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2179000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1992000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1928000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1859000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2311000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-4264000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2021000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2151000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1935000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>2017000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4151,8 +4235,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4195,130 +4280,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13989000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12038000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9129000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9445000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8028000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8810000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11973000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9011000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9301000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9708000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10944000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34741000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34248000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>31560000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7629000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9502000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5203000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6528000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7989000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11969000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6630000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6112000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6266000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9087000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9145000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7687000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6037000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11415000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5525000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7358000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6945000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>11956000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>10131000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>9741000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3800000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3000000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2629000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3358000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3241000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3485000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4359,621 +4448,636 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>1000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1676000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1976000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1980000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>48000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>952000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1452000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>4454000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4381000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3273000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2276000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>325000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2874000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>9438000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>16233000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>18943000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>22359000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>17965000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>19264000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>22431000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>37878000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>38351000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>36598000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>35040000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>34844000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>34495000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10227000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9138000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9570000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8490000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8701000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8132000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6782000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7317000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6934000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6776000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7942000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6145000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5830000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5736000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5563000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5326000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5327000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5077000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4895000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4765000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4479000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4423000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4525000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4094000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5366000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5009000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4057000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3606000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3801000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3771000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3580000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3441000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3504000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3633000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3237000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3404000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3560000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3248000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3165000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3186000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6220000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6186000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6225000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6346000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6583000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6729000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6998000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7362000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7995000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8724000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9518000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5026000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4978000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5011000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4930000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4757000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4554000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4411000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4086000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4152000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4115000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4017000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3893000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3942000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3840000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3682000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3584000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3243000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3176000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3016000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2940000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3017000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3063000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>2952000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2834000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2927000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2961000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2871000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2745000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2681000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4525000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4113000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1188000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3604000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3422000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3258000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1138000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3076000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2976000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2821000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>281000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2565000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2324000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2388000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2501000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2258000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2488000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2367000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2542000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2423000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2293000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2079000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2265000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2268000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2110000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1888000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3349000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2011000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2063000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1794000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1941000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2008000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1932000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1727000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2694000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1939000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2015000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1997000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34961000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31475000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29057000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27885000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26734000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26929000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29030000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26766000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27206000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28029000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30332000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>48477000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>47380000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>44703000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22186000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24062000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19322000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18520000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19385000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>24380000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19099000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21299000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21144000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22661000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22895000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18813000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18440000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>31051000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>30746000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>35151000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>37618000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>38320000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>37970000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>40689000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>49476000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>49752000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>48442000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>46456000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>46010000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>45844000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6501000</v>
+      </c>
+      <c r="E47" s="3">
         <v>6611000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6804000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7449000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5471000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6104000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4770000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5693000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4087000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4147000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5057000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4275000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4314000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5368000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5049,252 +5153,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8547000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8216000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8515000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7220000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6855000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6681000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7100000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6156000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6097000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6002000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6592000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5563000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5532000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5460000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5427000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5188000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5158000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5142000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5184000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4982000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4906000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4855000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4889000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4816000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4843000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4879000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5397000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5323000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5312000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5309000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4958000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4899000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4922000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4943000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4989000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4914000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4980000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4960000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4961000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4912000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>39155000</v>
+      </c>
+      <c r="E49" s="3">
         <v>40053000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>40956000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>41815000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>43288000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>44369000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46336000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>47578000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>48788000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>49942000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>51270000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>28659000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30164000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30924000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31609000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>28111000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>28792000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>29464000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>30072000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>29324000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>29984000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>30620000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>31276000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>31928000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>32626000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>33336000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34116000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21407000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>21502000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>21816000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>22142000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>22466000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>23167000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>23550000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>23370000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>23649000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>24327000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>24679000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>25030000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>25492000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5415,8 +5528,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5537,130 +5653,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6475000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6149000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5254000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5772000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5549000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5284000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4603000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4690000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4729000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4860000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3903000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3560000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2879000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2265000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5899000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6339000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6022000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6070000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6524000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6307000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5784000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5765000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5639000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5232000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4647000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4641000</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>1754000</v>
       </c>
       <c r="AD52" s="3">
         <v>1754000</v>
       </c>
       <c r="AE52" s="3">
+        <v>1754000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1813000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1721000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1698000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1648000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1625000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1982000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2119000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2016000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1838000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1767000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1625000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1902000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5781,130 +5903,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>95639000</v>
+      </c>
+      <c r="E54" s="3">
         <v>92504000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>90586000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90141000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>87897000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>89367000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>91839000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>90883000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>90907000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>92980000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97154000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>90534000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>90269000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>88720000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>65121000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>63700000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>59294000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>59196000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>61165000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64993000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59773000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>62539000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62948000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>64637000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>65011000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>61669000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59707000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>59535000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>59373000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>63997000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>66416000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>67333000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>67684000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>71164000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>79954000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>80331000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>79587000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>77862000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>77626000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>78150000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5947,8 +6075,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5991,198 +6120,202 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2865000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2935000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2367000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2838000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3010000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2406000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1908000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2147000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2267000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1628000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1590000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1358000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1212000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1320000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1572000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1204000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1256000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1403000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1366000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1171000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1277000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1396000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1421000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1161000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1150000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1338000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1371000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1005000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1001000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1091000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1207000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1042000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1026000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1089000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1352000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>879000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>883000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>902000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>917000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>825000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5445000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5437000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4734000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2153000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2444000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3368000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3657000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3544000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5528000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3959000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1562000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1428000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2167000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>834000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1591000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1543000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>817000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>844000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>87000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4288000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4324000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1556000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>91000</v>
       </c>
       <c r="Z58" s="3">
         <v>91000</v>
@@ -6191,52 +6324,55 @@
         <v>91000</v>
       </c>
       <c r="AB58" s="3">
+        <v>91000</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1840000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2953000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2049000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2816000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3705000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4419000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5077000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4288000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2183000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1152000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1999000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1459000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3799000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>4403000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>4797000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6244,10 +6380,10 @@
         <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>12343000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -6255,11 +6391,11 @@
       <c r="H59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="3">
         <v>12266000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>10</v>
@@ -6267,464 +6403,476 @@
       <c r="L59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N59" s="3">
         <v>2869000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>54000</v>
       </c>
-      <c r="O59" s="3" t="s">
+      <c r="P59" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>132000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12524000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11584000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10545000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10639000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10731000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9383000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8984000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9917000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10141000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8701000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9282000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8649000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8511000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7683000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6805000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7910000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7862000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6313000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5891000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7207000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>6516000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5315000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>5473000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>5822000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>5884000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>4920000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25502000</v>
+      </c>
+      <c r="E60" s="3">
         <v>24955000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25489000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21791000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20476000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23008000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23099000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20312000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21517000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19714000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18392000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16954000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17097000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14215000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>15687000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14331000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12618000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12886000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12184000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14842000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14585000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12869000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11653000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9953000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10523000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11827000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12835000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10737000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10622000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>12706000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13488000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>12432000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>11205000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>10479000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>9020000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>8193000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7815000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>10523000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>11204000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>10542000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>51859000</v>
+      </c>
+      <c r="E61" s="3">
         <v>51886000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50701000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52434000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53760000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54013000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>57222000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>56854000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57117000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>60061000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>63861000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>59040000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>59377000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>60761000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>37354000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>37161000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>35705000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>36010000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33222000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>33291000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28458000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31129000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>32895000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>34196000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>34133000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>30008000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>26950000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>27742000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27798000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>29319000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>29510000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>29350000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>30209000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33358000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>34190000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>33777000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>33603000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>30293000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>30193000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>30526000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5289000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5129000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4372000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4839000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4847000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4629000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4025000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4479000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4568000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6321000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6315000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6884000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7014000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8396000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8419000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8555000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8552000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9384000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9059000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8643000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8483000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9207000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>8991000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9529000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9696000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10349000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>10249000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>10129000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10159000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>11140000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10918000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11202000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11361000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>11707000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>11503000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6132000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6447000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>6409000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>6354000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>6309000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6845,8 +6993,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6967,8 +7118,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7089,130 +7243,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83951000</v>
+      </c>
+      <c r="E66" s="3">
         <v>83314000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>81928000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>80522000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>80469000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83160000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85962000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>83356000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>84982000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87958000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>90922000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>82878000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>83488000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>83372000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>61460000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>60047000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>56875000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58280000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>54465000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56776000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>51526000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>53205000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>53539000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>53678000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>54352000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>52184000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>50034000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48608000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>48579000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53165000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>53916000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>52984000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>52775000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>55544000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>54713000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>48102000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>47865000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>47225000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>47751000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>47377000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7255,8 +7415,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7377,8 +7538,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7499,8 +7663,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7621,8 +7788,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7743,130 +7913,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-22275000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-24650000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-25107000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-23800000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-25708000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-27140000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-27590000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-25530000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27124000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27870000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-26549000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-24971000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25540000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-26919000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-28622000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-28066000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-28252000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-29568000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-24600000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-22964000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-22762000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-21639000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-21408000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-19851000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-20168000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-21378000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-21330000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-20136000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-20054000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-19895000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-17977000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-15987000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-15266000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-14387000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-5072000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1774000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1378000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>233000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-438000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>221000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7987,8 +8163,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8109,8 +8288,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8231,130 +8413,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11688000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9190000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8658000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9619000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7428000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6207000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5877000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7527000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5925000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5022000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6232000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7656000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6781000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5348000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3661000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3653000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2419000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>916000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6700000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8217000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8247000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9334000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9409000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10959000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10659000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9485000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9673000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10927000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10794000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10832000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12500000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14349000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14909000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15620000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>25241000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>32229000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>31722000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>30637000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>29875000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>30773000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8475,257 +8663,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1819000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1333000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3216000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1432000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1730000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>627000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2830000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>746000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-113000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>767000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1730000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1379000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2841000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1616000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2143000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1317000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1476000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1899000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1884000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>464000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1646000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1615000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2021000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1803000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1703000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1968000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2179000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1992000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1928000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1859000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2296000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2311000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-4264000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2021000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2151000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2071000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1935000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>2017000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8768,130 +8965,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E83" s="3">
         <v>187000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>197000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>196000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>199000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>280000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>195000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>189000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>207000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>211000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>237000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>165000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>204000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>911000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>837000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>828000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>841000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>852000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>850000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>855000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>841000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>873000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>901000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>930000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>897000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>702000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>508000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>501000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>495000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>490000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>501000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>484000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>471000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>449000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>464000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>518000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>524000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>559000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>503000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9012,8 +9213,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9134,8 +9338,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9256,8 +9463,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9378,8 +9588,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9500,130 +9713,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4002000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2189000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1603000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4684000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2280000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1391000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4771000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3571000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2459000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>689000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>538000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2760000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4109000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2649000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2978000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1930000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2164000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2808000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2418000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1931000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2104000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2153000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3368000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2842000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2134000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2514000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3377000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1414000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1845000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3194000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3273000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2102000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2727000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3012000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3454000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2326000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2385000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3100000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2662000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9666,130 +9885,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-513000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-712000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-642000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-436000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-369000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-411000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-371000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-257000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-238000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-230000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-249000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-248000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-271000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-344000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-340000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-160000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-246000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-190000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-287000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-242000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-185000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-166000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-173000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-135000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-158000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-142000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-188000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-170000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-144000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-116000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-225000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-171000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-187000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-155000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-153000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-158000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-185000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-168000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-326000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9910,8 +10133,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10032,130 +10258,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-569000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-716000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-693000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-414000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-389000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-447000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-402000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-210000</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-217000</v>
       </c>
       <c r="L94" s="3">
         <v>-217000</v>
       </c>
       <c r="M94" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="N94" s="3">
         <v>-27089000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-262000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-211000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1358000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3473000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-267000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2193000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-111000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-230000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>73000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1209000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-319000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1384000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1628000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2159000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5963000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5372000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2745000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>3555000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4637000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1132000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2938000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>14906000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-78000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1976000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1813000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-157000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2389000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10198,130 +10430,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1362000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1358000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1283000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1282000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1280000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1279000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1205000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1210000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1209000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1208000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>1140000</v>
       </c>
       <c r="N96" s="3">
         <v>1140000</v>
       </c>
       <c r="O96" s="3">
+        <v>1140000</v>
+      </c>
+      <c r="P96" s="3">
         <v>1139000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1040000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-1038000</v>
       </c>
       <c r="S96" s="3">
         <v>-1038000</v>
       </c>
       <c r="T96" s="3">
+        <v>-1038000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-990000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-999000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1008000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1016000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-932000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-936000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-942000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-945000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-860000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-868000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-880000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-901000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-840000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-851000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-865000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-951000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-834000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-838000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-846000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-847000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-747000</v>
       </c>
       <c r="AP96" s="3">
         <v>-747000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-747000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10442,8 +10678,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10564,8 +10803,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10686,130 +10928,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1482000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1436000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1226000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2853000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2673000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4107000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1407000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3651000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2649000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1708000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2754000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2005000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1210000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21509000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1049000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1588000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1062000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3514000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6558000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2848000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2622000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1939000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3590000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1798000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>775000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-254000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1929000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2859000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5992000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4987000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3568000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2580000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4650000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-11692000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2134000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1107000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1242000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2111000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2122000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>582000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10852,8 +11100,8 @@
       <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10930,126 +11178,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1951000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2909000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-316000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1417000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-782000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3163000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2962000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-290000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-407000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1236000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23797000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>493000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2688000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23931000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1873000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4299000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1325000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1461000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3980000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5339000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>518000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-154000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2821000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-58000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1458000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1650000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5378000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5890000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1833000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>413000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5011000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1825000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>390000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>5941000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>800000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>371000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-729000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>117000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-244000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>855000</v>
       </c>
     </row>
